--- a/output/pdf_financials_xlsx/FREQ.xlsx
+++ b/output/pdf_financials_xlsx/FREQ.xlsx
@@ -2841,19 +2841,19 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.051803</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.111994</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.957521</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.303619</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.646608</v>
       </c>
       <c r="G92" s="1" t="inlineStr">
         <is>
@@ -4910,7 +4910,11 @@
           <t>Share-based payments reserve 15</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -5356,7 +5360,11 @@
           <t>Share-based payments reserve 16</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -6006,7 +6014,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" s="5" t="n">
         <v>0.051803</v>
       </c>

--- a/output/pdf_financials_xlsx/FREQ.xlsx
+++ b/output/pdf_financials_xlsx/FREQ.xlsx
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.033353</v>
+        <v>0.116581</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>1.107735</v>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.033353</v>
+        <v>-0.116581</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-0.784241</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000499</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.016908</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1101,10 +1101,10 @@
         <v>-0.116581</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.777586</v>
+        <v>-0.778085</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.85839</v>
+        <v>-4.875298</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.435555</v>
@@ -1151,10 +1151,10 @@
         <v>-0.116581</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.761055</v>
+        <v>-0.761554</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.825738</v>
+        <v>-4.842646</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.400407</v>
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-90.01369623223511</v>
+        <v>-90.07271540222924</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-690.2865431159274</v>
+        <v>-692.7051089127038</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>-168.7847414728215</v>
@@ -1259,19 +1259,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.434818</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.173889</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.958761</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.131898</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.33563</v>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
@@ -1313,19 +1313,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.434818</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.173889</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.958761</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.131898</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.33563</v>
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
@@ -1637,19 +1637,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.434818</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.19821</v>
+        <v>0.024321</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.983162</v>
+        <v>0.024401</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.137473</v>
+        <v>0.005575</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.424936</v>
+        <v>0.089306</v>
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E156" s="5" t="n">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">

--- a/output/pdf_financials_xlsx/FREQ.xlsx
+++ b/output/pdf_financials_xlsx/FREQ.xlsx
@@ -1273,10 +1273,8 @@
       <c r="F34" s="3" t="n">
         <v>0.33563</v>
       </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G34" s="3" t="n">
+        <v>1.134337</v>
       </c>
     </row>
     <row r="35">
@@ -1300,10 +1298,8 @@
       <c r="F35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1327,10 +1323,8 @@
       <c r="F36" s="3" t="n">
         <v>0.33563</v>
       </c>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G36" s="3" t="n">
+        <v>1.134337</v>
       </c>
     </row>
     <row r="37">
@@ -1354,10 +1348,8 @@
       <c r="F37" s="3" t="n">
         <v>0.035699</v>
       </c>
-      <c r="G37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G37" s="3" t="n">
+        <v>0.020501</v>
       </c>
     </row>
     <row r="38">
@@ -1381,10 +1373,8 @@
       <c r="F38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1408,10 +1398,8 @@
       <c r="F39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1435,10 +1423,8 @@
       <c r="F40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1462,10 +1448,8 @@
       <c r="F41" s="3" t="n">
         <v>0.035699</v>
       </c>
-      <c r="G41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G41" s="3" t="n">
+        <v>0.020501</v>
       </c>
     </row>
     <row r="42">
@@ -1489,10 +1473,8 @@
       <c r="F42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1516,10 +1498,8 @@
       <c r="F43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1543,10 +1523,8 @@
       <c r="F44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1570,10 +1548,8 @@
       <c r="F45" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1597,10 +1573,8 @@
       <c r="F46" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1624,10 +1598,8 @@
       <c r="F47" s="3" t="n">
         <v>0.04191</v>
       </c>
-      <c r="G47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G47" s="3" t="n">
+        <v>0.124068</v>
       </c>
     </row>
     <row r="48">
@@ -1651,10 +1623,8 @@
       <c r="F48" s="3" t="n">
         <v>0.089306</v>
       </c>
-      <c r="G48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G48" s="3" t="n">
+        <v>0.060845</v>
       </c>
     </row>
     <row r="49">
@@ -1678,10 +1648,8 @@
       <c r="F49" s="3" t="n">
         <v>0.502545</v>
       </c>
-      <c r="G49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G49" s="3" t="n">
+        <v>1.339751</v>
       </c>
     </row>
     <row r="50">
@@ -1705,10 +1673,8 @@
       <c r="F50" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1732,10 +1698,8 @@
       <c r="F51" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1759,10 +1723,8 @@
       <c r="F52" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1786,10 +1748,8 @@
       <c r="F53" s="3" t="n">
         <v>0.003465</v>
       </c>
-      <c r="G53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G53" s="3" t="n">
+        <v>0.001485</v>
       </c>
     </row>
     <row r="54">
@@ -1813,10 +1773,8 @@
       <c r="F54" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1877,10 +1835,8 @@
       <c r="F56" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1904,10 +1860,8 @@
       <c r="F57" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1931,10 +1885,8 @@
       <c r="F58" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1958,10 +1910,8 @@
       <c r="F59" s="3" t="n">
         <v>0.098409</v>
       </c>
-      <c r="G59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G59" s="3" t="n">
+        <v>0.065551</v>
       </c>
     </row>
     <row r="60">
@@ -1985,10 +1935,8 @@
       <c r="F60" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -2012,10 +1960,8 @@
       <c r="F61" s="3" t="n">
         <v>0.003465</v>
       </c>
-      <c r="G61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G61" s="3" t="n">
+        <v>0.001485</v>
       </c>
     </row>
     <row r="62">
@@ -2039,10 +1985,8 @@
       <c r="F62" s="3" t="n">
         <v>0.101874</v>
       </c>
-      <c r="G62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G62" s="3" t="n">
+        <v>0.067036</v>
       </c>
     </row>
     <row r="63">
@@ -2066,10 +2010,8 @@
       <c r="F63" s="3" t="n">
         <v>0.604419</v>
       </c>
-      <c r="G63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G63" s="3" t="n">
+        <v>1.406787</v>
       </c>
     </row>
     <row r="64">
@@ -2093,10 +2035,8 @@
       <c r="F64" s="3" t="n">
         <v>0.386746</v>
       </c>
-      <c r="G64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G64" s="3" t="n">
+        <v>0.258092</v>
       </c>
     </row>
     <row r="65">
@@ -2120,10 +2060,8 @@
       <c r="F65" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2147,10 +2085,8 @@
       <c r="F66" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G66" s="3" t="n">
+        <v>0.013998</v>
       </c>
     </row>
     <row r="67">
@@ -2174,10 +2110,8 @@
       <c r="F67" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G67" s="3" t="n">
+        <v>0.06375</v>
       </c>
     </row>
     <row r="68">
@@ -2201,10 +2135,8 @@
       <c r="F68" s="3" t="n">
         <v>0.386746</v>
       </c>
-      <c r="G68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G68" s="3" t="n">
+        <v>0.321842</v>
       </c>
     </row>
     <row r="69">
@@ -2228,10 +2160,8 @@
       <c r="F69" s="3" t="n">
         <v>0.051343</v>
       </c>
-      <c r="G69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G69" s="3" t="n">
+        <v>0.055236</v>
       </c>
     </row>
     <row r="70">
@@ -2255,10 +2185,8 @@
       <c r="F70" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -2282,10 +2210,8 @@
       <c r="F71" s="3" t="n">
         <v>0.051343</v>
       </c>
-      <c r="G71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G71" s="3" t="n">
+        <v>0.055236</v>
       </c>
     </row>
     <row r="72">
@@ -2309,10 +2235,8 @@
       <c r="F72" s="3" t="n">
         <v>0.013924</v>
       </c>
-      <c r="G72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G72" s="3" t="n">
+        <v>0.006435</v>
       </c>
     </row>
     <row r="73">
@@ -2336,10 +2260,8 @@
       <c r="F73" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2363,10 +2285,8 @@
       <c r="F74" s="3" t="n">
         <v>0.013924</v>
       </c>
-      <c r="G74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G74" s="3" t="n">
+        <v>0.006435</v>
       </c>
     </row>
     <row r="75">
@@ -2390,10 +2310,8 @@
       <c r="F75" s="3" t="n">
         <v>0.545341</v>
       </c>
-      <c r="G75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G75" s="3" t="n">
+        <v>0.38001</v>
       </c>
     </row>
     <row r="76">
@@ -2419,10 +2337,8 @@
       <c r="F76" s="3" t="n">
         <v>0.997354</v>
       </c>
-      <c r="G76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G76" s="3" t="n">
+        <v>0.763523</v>
       </c>
     </row>
     <row r="77">
@@ -2446,10 +2362,8 @@
       <c r="F77" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2473,10 +2387,8 @@
       <c r="F78" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2500,10 +2412,8 @@
       <c r="F79" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2529,10 +2439,8 @@
       <c r="F80" s="3" t="n">
         <v>-0.1155650291033992</v>
       </c>
-      <c r="G80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G80" s="3" t="n">
+        <v>0.08586832156004377</v>
       </c>
     </row>
     <row r="81">
@@ -2556,10 +2464,8 @@
       <c r="F81" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2583,10 +2489,8 @@
       <c r="F82" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2610,10 +2514,8 @@
       <c r="F83" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2637,10 +2539,8 @@
       <c r="F84" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2664,10 +2564,8 @@
       <c r="F85" s="3" t="n">
         <v>0.051343</v>
       </c>
-      <c r="G85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -2693,10 +2591,8 @@
       <c r="F86" s="3" t="n">
         <v>0.051343</v>
       </c>
-      <c r="G86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G86" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -2720,10 +2616,8 @@
       <c r="F87" s="3" t="n">
         <v>1.048697</v>
       </c>
-      <c r="G87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G87" s="3" t="n">
+        <v>0.763523</v>
       </c>
     </row>
     <row r="88">
@@ -2747,10 +2641,8 @@
       <c r="F88" s="3" t="n">
         <v>7.400139</v>
       </c>
-      <c r="G88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G88" s="3" t="n">
+        <v>9.847001000000001</v>
       </c>
     </row>
     <row r="89">
@@ -2774,10 +2666,8 @@
       <c r="F89" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2801,10 +2691,8 @@
       <c r="F90" s="3" t="n">
         <v>-9.594550999999999</v>
       </c>
-      <c r="G90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G90" s="3" t="n">
+        <v>-11.285352</v>
       </c>
     </row>
     <row r="91">
@@ -2828,10 +2716,8 @@
       <c r="F91" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2855,10 +2741,8 @@
       <c r="F92" s="3" t="n">
         <v>1.646608</v>
       </c>
-      <c r="G92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G92" s="3" t="n">
+        <v>2.081615</v>
       </c>
     </row>
     <row r="93">
@@ -2882,10 +2766,8 @@
       <c r="F93" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2909,10 +2791,8 @@
       <c r="F94" s="3" t="n">
         <v>-0.444278</v>
       </c>
-      <c r="G94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G94" s="3" t="n">
+        <v>0.6432639999999999</v>
       </c>
     </row>
     <row r="95">
@@ -2936,10 +2816,8 @@
       <c r="F95" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2963,10 +2841,8 @@
       <c r="F96" s="3" t="n">
         <v>-0.444278</v>
       </c>
-      <c r="G96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G96" s="3" t="n">
+        <v>0.6432639999999999</v>
       </c>
     </row>
     <row r="97">
@@ -2990,10 +2866,8 @@
       <c r="F97" s="3" t="n">
         <v>-0.7350496923491816</v>
       </c>
-      <c r="G97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G97" s="3" t="n">
+        <v>0.4572575663551056</v>
       </c>
     </row>
     <row r="98">
@@ -3024,10 +2898,8 @@
       <c r="F99" s="3" t="n">
         <v>-1.181257</v>
       </c>
-      <c r="G99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G99" s="3" t="n">
+        <v>-1.690801</v>
       </c>
     </row>
     <row r="100">
@@ -3051,10 +2923,8 @@
       <c r="F100" s="3" t="n">
         <v>0.032062</v>
       </c>
-      <c r="G100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G100" s="3" t="n">
+        <v>0.034838</v>
       </c>
     </row>
     <row r="101">
@@ -3078,10 +2948,8 @@
       <c r="F101" s="3" t="n">
         <v>-0.021034</v>
       </c>
-      <c r="G101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G101" s="3" t="n">
+        <v>0.015198</v>
       </c>
     </row>
     <row r="102">
@@ -3105,10 +2973,8 @@
       <c r="F102" s="3" t="n">
         <v>0.045155</v>
       </c>
-      <c r="G102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G102" s="3" t="n">
+        <v>-0.08215799999999999</v>
       </c>
     </row>
     <row r="103">
@@ -3132,10 +2998,8 @@
       <c r="F103" s="3" t="n">
         <v>-0.019024</v>
       </c>
-      <c r="G103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G103" s="3" t="n">
+        <v>-0.011247</v>
       </c>
     </row>
     <row r="104">
@@ -3159,10 +3023,8 @@
       <c r="F104" s="3" t="n">
         <v>0.153928</v>
       </c>
-      <c r="G104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G104" s="3" t="n">
+        <v>-0.128653</v>
       </c>
     </row>
     <row r="105">
@@ -3186,10 +3048,8 @@
       <c r="F105" s="3" t="n">
         <v>-0.023139</v>
       </c>
-      <c r="G105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G105" s="3" t="n">
+        <v>-0.007489</v>
       </c>
     </row>
     <row r="106">
@@ -3213,10 +3073,8 @@
       <c r="F106" s="3" t="n">
         <v>0.135886</v>
       </c>
-      <c r="G106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G106" s="3" t="n">
+        <v>-0.214349</v>
       </c>
     </row>
     <row r="107">
@@ -3240,10 +3098,8 @@
       <c r="F107" s="3" t="n">
         <v>0.347537</v>
       </c>
-      <c r="G107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G107" s="3" t="n">
+        <v>0.555694</v>
       </c>
     </row>
     <row r="108">
@@ -3267,10 +3123,8 @@
       <c r="F108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -3294,10 +3148,8 @@
       <c r="F109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3310,7 +3162,7 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -3321,10 +3173,8 @@
       <c r="F110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3346,12 +3196,10 @@
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.00396</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -3375,10 +3223,8 @@
       <c r="F112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -3402,10 +3248,8 @@
       <c r="F113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -3429,10 +3273,8 @@
       <c r="F114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -3456,10 +3298,8 @@
       <c r="F115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3483,10 +3323,8 @@
       <c r="F116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -3510,10 +3348,8 @@
       <c r="F117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -3537,10 +3373,8 @@
       <c r="F118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -3564,10 +3398,8 @@
       <c r="F119" s="3" t="n">
         <v>-0.007057</v>
       </c>
-      <c r="G119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G119" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -3591,10 +3423,8 @@
       <c r="F120" s="3" t="n">
         <v>0.07316499999999999</v>
       </c>
-      <c r="G120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G120" s="3" t="n">
+        <v>0.056</v>
       </c>
     </row>
     <row r="121">
@@ -3618,10 +3448,8 @@
       <c r="F121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -3645,10 +3473,8 @@
       <c r="F122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -3672,10 +3498,8 @@
       <c r="F123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3699,10 +3523,8 @@
       <c r="F124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3726,10 +3548,8 @@
       <c r="F125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3753,10 +3573,8 @@
       <c r="F126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3817,10 +3635,8 @@
       <c r="F128" s="3" t="n">
         <v>-0.027853</v>
       </c>
-      <c r="G128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G128" s="3" t="n">
+        <v>-0.033885</v>
       </c>
     </row>
     <row r="129">
@@ -3844,10 +3660,8 @@
       <c r="F129" s="3" t="n">
         <v>0.886915</v>
       </c>
-      <c r="G129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G129" s="3" t="n">
+        <v>2.021445</v>
       </c>
     </row>
     <row r="130">
@@ -3871,10 +3685,8 @@
       <c r="F130" s="3" t="n">
         <v>0.131898</v>
       </c>
-      <c r="G130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G130" s="3" t="n">
+        <v>0.33563</v>
       </c>
     </row>
     <row r="131">
@@ -3898,10 +3710,8 @@
       <c r="F131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3925,10 +3735,8 @@
       <c r="F132" s="3" t="n">
         <v>0.203732</v>
       </c>
-      <c r="G132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G132" s="3" t="n">
+        <v>0.7987069999999999</v>
       </c>
     </row>
     <row r="133">
@@ -3952,10 +3760,8 @@
       <c r="F133" s="3" t="n">
         <v>0.33563</v>
       </c>
-      <c r="G133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G133" s="3" t="n">
+        <v>1.134337</v>
       </c>
     </row>
     <row r="134">
@@ -3977,12 +3783,10 @@
         <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.00396</v>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -4004,12 +3808,10 @@
         <v>-1.125804</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-0.676126</v>
-      </c>
-      <c r="G135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.680086</v>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>-1.222738</v>
       </c>
     </row>
   </sheetData>
@@ -4023,7 +3825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J170"/>
+  <dimension ref="A1:J177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4126,10 +3928,8 @@
       <c r="I2" s="5" t="n">
         <v>0.33563</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J2" s="5" t="n">
+        <v>1.134337</v>
       </c>
     </row>
     <row r="3">
@@ -4170,10 +3970,8 @@
       <c r="I3" s="5" t="n">
         <v>0.035699</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J3" s="5" t="n">
+        <v>0.020501</v>
       </c>
     </row>
     <row r="4">
@@ -4214,10 +4012,8 @@
       <c r="I4" s="5" t="n">
         <v>0.049598</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J4" s="5" t="n">
+        <v>0.060845</v>
       </c>
     </row>
     <row r="5">
@@ -4258,10 +4054,8 @@
       <c r="I5" s="5" t="n">
         <v>0.04191</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J5" s="5" t="n">
+        <v>0.124068</v>
       </c>
     </row>
     <row r="6">
@@ -4348,10 +4142,8 @@
       <c r="I7" s="5" t="n">
         <v>0.502545</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J7" s="5" t="n">
+        <v>1.339751</v>
       </c>
     </row>
     <row r="8">
@@ -4396,10 +4188,8 @@
       <c r="I8" s="5" t="n">
         <v>0.003465</v>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J8" s="5" t="n">
+        <v>0.001485</v>
       </c>
     </row>
     <row r="9">
@@ -4440,10 +4230,8 @@
       <c r="I9" s="5" t="n">
         <v>0.098409</v>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J9" s="5" t="n">
+        <v>0.065551</v>
       </c>
     </row>
     <row r="10">
@@ -4484,10 +4272,8 @@
       <c r="I10" s="5" t="n">
         <v>0.604419</v>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J10" s="5" t="n">
+        <v>1.406787</v>
       </c>
     </row>
     <row r="11">
@@ -4503,7 +4289,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Trade and other payables 9 $</t>
+          <t>Trade and other payables 9&amp;13 $</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4516,22 +4302,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="5" t="n">
-        <v>0.100443</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>0.181329</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>0.232818</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I11" s="5" t="n">
         <v>0.386746</v>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J11" s="5" t="n">
+        <v>0.258092</v>
       </c>
     </row>
     <row r="12">
@@ -4547,12 +4337,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Deferred revenue 10</t>
+          <t>Due to related parties 13</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CurrentDeferredRevenue</t>
+          <t>OtherPayable</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -4560,22 +4350,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="5" t="n">
-        <v>0.109462</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>0.135156</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>0.037063</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>0.013924</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>0.013998</v>
       </c>
     </row>
     <row r="13">
@@ -4591,37 +4387,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Amounts due to related party 13</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Deferred revenue 10</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CurrentDeferredRevenue</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F13" s="5" t="n">
+        <v>0.109462</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.135156</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.0182</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.037063</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>0.013924</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>0.006435</v>
       </c>
     </row>
     <row r="14">
@@ -4660,10 +4452,8 @@
       <c r="I14" s="5" t="n">
         <v>0.596684</v>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J14" s="5" t="n">
+        <v>0.429762</v>
       </c>
     </row>
     <row r="15">
@@ -4679,12 +4469,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Current liabilities total</t>
+          <t>CEBA loan payable 12</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CurrentLiabilities</t>
+          <t>CurrentDebt</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -4692,22 +4482,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="5" t="n">
-        <v>2.353474</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1.06277</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>0.840328</v>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v>0.997354</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.06</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>0.055236</v>
       </c>
     </row>
     <row r="16">
@@ -4718,17 +4512,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Non-current liabilities</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CEBA loan payable 12</t>
+          <t>Current liabilities total</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CurrentDebt</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -4737,23 +4531,19 @@
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.051976</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.353474</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>1.06277</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0.048226</v>
+        <v>0.840328</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.051343</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.997354</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>0.763523</v>
       </c>
     </row>
     <row r="17">
@@ -4769,12 +4559,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Total liabilities</t>
+          <t>CEBA loan payable</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TotalLiabilities</t>
+          <t>CurrentDebt</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -4782,17 +4572,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F17" s="5" t="n">
-        <v>2.409862</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>1.06277</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>0.888554</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I17" s="5" t="n">
-        <v>1.048697</v>
+        <v>0.051343</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -4808,17 +4604,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Equity (deficit)</t>
+          <t>Non-current liabilities</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Share capital 14</t>
+          <t>Total liabilities</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CapitalStock</t>
+          <t>TotalLiabilities</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -4826,26 +4622,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F18" s="5" t="n">
+        <v>2.409862</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>1.06277</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>6.587203</v>
+        <v>0.888554</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>7.400139</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.048697</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>0.763523</v>
       </c>
     </row>
     <row r="19">
@@ -4861,10 +4651,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Share subscriptions 14</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Share capital 14</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -4880,18 +4674,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H19" s="5" t="n">
+        <v>6.587203</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>0.103526</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.400139</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>9.847001000000001</v>
       </c>
     </row>
     <row r="20">
@@ -4907,14 +4697,10 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Share-based payments reserve 15</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>AdditionalPaidInCapital</t>
-        </is>
-      </c>
+          <t>Share subscriptions 14</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -4930,11 +4716,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H20" s="5" t="n">
-        <v>1.303619</v>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I20" s="5" t="n">
-        <v>1.646608</v>
+        <v>0.103526</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -4955,12 +4743,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>Share-based payments reserve 15</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>RetainedEarnings</t>
+          <t>AdditionalPaidInCapital</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -4968,22 +4756,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F21" s="5" t="n">
-        <v>-2.119349</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>-6.977739</v>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-8.413294</v>
+        <v>1.303619</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>-9.594550999999999</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.646608</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>2.081615</v>
       </c>
     </row>
     <row r="22">
@@ -4999,31 +4789,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Total equity (deficit)</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Deficit</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-2.007255</v>
+        <v>-2.119349</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.334038</v>
+        <v>-6.977739</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-0.522472</v>
+        <v>-8.413294</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>-0.444278</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-9.594550999999999</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>-11.285352</v>
       </c>
     </row>
     <row r="23">
@@ -5039,35 +4831,29 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Total liabilities and equity $</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
-        </is>
-      </c>
+          <t>Total equity (deficit)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.402607</v>
+        <v>-2.007255</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>1.396808</v>
+        <v>0.334038</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>0.366082</v>
+        <v>-0.522472</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>0.604419</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.444278</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>0.6432639999999999</v>
       </c>
     </row>
     <row r="24">
@@ -5078,40 +4864,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Equity (deficit)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cash $</t>
+          <t>Total liabilities and equity $</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CashAndCashEquivalents</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>0.434818</v>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.173889</v>
+        <v>0.402607</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.958761</v>
+        <v>1.396808</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>0.131898</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.366082</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>0.604419</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>1.406787</v>
       </c>
     </row>
     <row r="25">
@@ -5122,17 +4906,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Right-of-use asset 13</t>
+          <t>Trade and other payables 9 $</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NetPPE</t>
+          <t>AccountsPayable</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -5141,20 +4925,16 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.017002</v>
+        <v>0.100443</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.00384</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.181329</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>0.232818</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>0.386746</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -5175,7 +4955,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Amounts due to related party 14</t>
+          <t>Amounts due to related party 13</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -5184,11 +4964,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F26" s="5" t="n">
-        <v>1.552879</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>0.016553</v>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H26" s="5" t="n">
         <v>0.0182</v>
@@ -5212,7 +4996,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Non-current liabilities</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -5230,23 +5014,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F27" s="5" t="n">
+        <v>0.051976</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>0.048226</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>0.051343</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -5262,30 +5042,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lease liability – current portion 13</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash $</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0.434818</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.01766</v>
+        <v>0.173889</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.00468</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.958761</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0.131898</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -5306,17 +5086,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Equity (deficit)</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Share capital 15</t>
+          <t>Right-of-use asset 13</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CapitalStock</t>
+          <t>NetPPE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -5325,13 +5105,15 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.017002</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>6.354256</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>6.587203</v>
+        <v>0.00384</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -5352,32 +5134,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Equity (deficit)</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Share-based payments reserve 16</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>AdditionalPaidInCapital</t>
-        </is>
-      </c>
+          <t>Amounts due to related party 14</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.111994</v>
+        <v>1.552879</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.957521</v>
+        <v>0.016553</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>1.303619</v>
+        <v>0.0182</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -5398,12 +5176,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Non-current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Deposits</t>
+          <t>Lease liability – current portion 13</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -5413,12 +5191,10 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.016125</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.01766</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.00468</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -5444,30 +5220,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Equity (deficit)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Convertible notes payable 11</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>Share capital 15</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.57303</v>
+        <v>0.0001</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.665052</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.354256</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>6.587203</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -5488,32 +5266,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Non-current liabilities</t>
+          <t>Equity (deficit)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lease liability 13</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>Share-based payments reserve 16</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.004412</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.111994</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.957521</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>1.303619</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -5532,18 +5310,24 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Non-current assets</t>
+        </is>
+      </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Notes October 31, 2021 October</t>
+          <t>Deposits</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" s="5" t="n">
-        <v>0.00202</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.016125</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -5574,31 +5358,25 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>PrepaidAssets</t>
-        </is>
-      </c>
+          <t>Convertible notes payable 11</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.00091</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.57303</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.665052</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -5624,26 +5402,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>Non-current liabilities</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Loan receivable 4</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>LoansReceivable</t>
-        </is>
-      </c>
+          <t>Lease liability 13</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.025127</v>
+        <v>0.004412</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -5672,26 +5446,18 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Current assets</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Total current assets</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>CurrentAssets</t>
-        </is>
-      </c>
+          <t>Notes October 31, 2021 October</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" s="5" t="n">
-        <v>0.434818</v>
+        <v>0.00202</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.416602</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -5727,17 +5493,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Deferred charges 12</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>Prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.093949</v>
+        <v>0.00091</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -5773,19 +5543,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Total assets $</t>
+          <t>Loan receivable 4</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>TotalAssets</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>0.434818</v>
+          <t>LoansReceivable</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.510551</v>
+        <v>0.025127</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -5816,24 +5588,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Trade payables and accrued liabilities 5 $</t>
+          <t>Total current assets</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CurrentAccruedExpenses</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0.022</v>
+        <v>0.434818</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.085059</v>
+        <v>0.416602</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -5864,12 +5636,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Subscriptions 6</t>
+          <t>Deferred charges 12</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -5879,7 +5651,7 @@
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.1105</v>
+        <v>0.093949</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -5910,24 +5682,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Total liabilities</t>
+          <t>Total assets $</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>TotalLiabilities</t>
+          <t>TotalAssets</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.022</v>
+        <v>0.434818</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.195559</v>
+        <v>0.510551</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -5958,24 +5730,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Shareholders' equity</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Share capital 7</t>
+          <t>Trade payables and accrued liabilities 5 $</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CapitalStock</t>
+          <t>CurrentAccruedExpenses</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0.482979</v>
+        <v>0.022</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.482979</v>
+        <v>0.085059</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -6006,24 +5778,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Shareholders' equity</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Reserves 7</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>AdditionalPaidInCapital</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="n">
-        <v>0.051803</v>
+          <t>Subscriptions 6</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.051803</v>
+        <v>0.1105</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -6054,24 +5824,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Shareholders' equity</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>Total liabilities</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>RetainedEarnings</t>
+          <t>TotalLiabilities</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>-0.121964</v>
+        <v>0.022</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>-0.21979</v>
+        <v>0.195559</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -6107,19 +5877,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Total shareholders' equity</t>
+          <t>Share capital 7</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>StockholdersEquity</t>
+          <t>CapitalStock</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0.412818</v>
+        <v>0.482979</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.314992</v>
+        <v>0.482979</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -6155,19 +5925,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Total liabilities and shareholders' equity $</t>
+          <t>Reserves 7</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+          <t>AdditionalPaidInCapital</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0.434818</v>
+        <v>0.051803</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.510551</v>
+        <v>0.051803</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -6193,40 +5963,44 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
+          <t>Shareholders' equity</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Net loss for the year $</t>
+          <t>Deficit</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>-0.121964</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>-0.777586</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>-4.85839</v>
-      </c>
-      <c r="H48" s="5" t="n">
-        <v>-1.435555</v>
-      </c>
-      <c r="I48" s="5" t="n">
-        <v>-1.181257</v>
+        <v>-0.21979</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -6237,40 +6011,44 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Shareholders' equity</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Depreciation and amortization</t>
+          <t>Total shareholders' equity</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0.412818</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.016531</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>0.032652</v>
-      </c>
-      <c r="H49" s="5" t="n">
-        <v>0.035148</v>
-      </c>
-      <c r="I49" s="5" t="n">
-        <v>0.032062</v>
+        <v>0.314992</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -6281,38 +6059,44 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Shareholders' equity</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Loan interest</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>0.097787</v>
-      </c>
-      <c r="H50" s="5" t="n">
-        <v>0.05343</v>
-      </c>
-      <c r="I50" s="5" t="n">
-        <v>0.044404</v>
+          <t>Total liabilities and shareholders' equity $</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0.434818</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>0.510551</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -6328,40 +6112,38 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Interest free benefit on CEBA loan</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>Net loss for the year $</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>-0.0138</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.777586</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>-4.85839</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>-0.011774</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.435555</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>-1.181257</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>-1.690801</v>
       </c>
     </row>
     <row r="52">
@@ -6377,35 +6159,33 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Provision on trade receivable</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>Depreciation and amortization</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.007145</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.016531</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.032652</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>0.001566</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.035148</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>0.032062</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>0.034838</v>
       </c>
     </row>
     <row r="53">
@@ -6421,7 +6201,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Gain on settlement of trade payable</t>
+          <t>Loan interest</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -6435,23 +6215,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G53" s="5" t="n">
+        <v>0.097787</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>-0.0126</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.05343</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>0.044404</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>0.038174</v>
       </c>
     </row>
     <row r="54">
@@ -6467,37 +6241,33 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Loss on debt modification</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>Share-based payments</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F54" s="5" t="n">
+        <v>0.037994</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.644845</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>0.109189</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>0.00315</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.347537</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>0.555694</v>
       </c>
     </row>
     <row r="55">
@@ -6508,17 +6278,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Share-based payments</t>
+          <t>Trade and other receivables</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>ChangeInReceivables</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6527,21 +6297,19 @@
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0.037994</v>
+        <v>0.06644799999999999</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.644845</v>
+        <v>-0.047251</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>0.109189</v>
+        <v>0.034881</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>0.347537</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.021034</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>0.015198</v>
       </c>
     </row>
     <row r="56">
@@ -6557,12 +6325,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Trade and other receivables</t>
+          <t>Prepaid expenses and deposits</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6571,21 +6339,19 @@
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.06644799999999999</v>
+        <v>-0.049448</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.047251</v>
+        <v>0.21006</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>0.034881</v>
+        <v>0.018826</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>-0.021034</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.019024</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>-0.011247</v>
       </c>
     </row>
     <row r="57">
@@ -6601,12 +6367,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Prepaid expenses and deposits</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>ChangeInInventory</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6615,21 +6381,19 @@
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>-0.049448</v>
+        <v>-0.114364</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.21006</v>
+        <v>-0.08590200000000001</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>0.018826</v>
+        <v>0.113442</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>-0.019024</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.045155</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>-0.08215799999999999</v>
       </c>
     </row>
     <row r="58">
@@ -6645,12 +6409,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Inventory</t>
+          <t>Trade and other payables</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ChangeInInventory</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6659,21 +6423,19 @@
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>-0.114364</v>
+        <v>-0.014896</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.08590200000000001</v>
+        <v>0.040042</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>0.113442</v>
+        <v>0.06408899999999999</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>0.045155</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.153928</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>-0.128653</v>
       </c>
     </row>
     <row r="59">
@@ -6689,12 +6451,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Trade and other payables</t>
+          <t>Deferred revenue</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>ChangeInOtherWorkingCapital</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6702,22 +6464,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F59" s="5" t="n">
-        <v>-0.014896</v>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.040042</v>
+        <v>0.025694</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>0.06408899999999999</v>
+        <v>-0.098093</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>0.153928</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.023139</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>-0.007489</v>
       </c>
     </row>
     <row r="60">
@@ -6733,14 +6495,10 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Deferred revenue</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>ChangeInOtherWorkingCapital</t>
-        </is>
-      </c>
+          <t>Amounts due (from) to related parties</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -6751,19 +6509,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G60" s="5" t="n">
-        <v>0.025694</v>
-      </c>
-      <c r="H60" s="5" t="n">
-        <v>-0.098093</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I60" s="5" t="n">
-        <v>-0.023139</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.057908</v>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>0.053706</v>
       </c>
     </row>
     <row r="61">
@@ -6779,35 +6539,31 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Amounts due from (to) related parties</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>-0.05858</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>-0.426489</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>-1.499172</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>0.001647</v>
+        <v>-1.125804</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>-0.057908</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.676126</v>
+      </c>
+      <c r="J61" s="5" t="n">
+        <v>-1.222738</v>
       </c>
     </row>
     <row r="62">
@@ -6818,33 +6574,41 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
+          <t>Purchase of equipment</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="n">
-        <v>-0.05858</v>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>-0.426489</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>-1.499172</v>
-      </c>
-      <c r="H62" s="5" t="n">
-        <v>-1.125804</v>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I62" s="5" t="n">
-        <v>-0.676126</v>
+        <v>-0.00396</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -6865,7 +6629,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Purchase of equipment</t>
+          <t>Intangible assets</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -6879,10 +6643,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G63" s="5" t="n">
+        <v>-0.15</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -6890,7 +6652,7 @@
         </is>
       </c>
       <c r="I63" s="5" t="n">
-        <v>-0.00396</v>
+        <v>-0.003097</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -6911,10 +6673,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Intangible assets</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>Net cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -6934,7 +6700,7 @@
         </is>
       </c>
       <c r="I64" s="5" t="n">
-        <v>-0.003097</v>
+        <v>-0.007057</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -6950,19 +6716,15 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Proceeds from issuance of share capital</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -6974,20 +6736,16 @@
         </is>
       </c>
       <c r="G65" s="5" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.544375</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>0.473817</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>-0.007057</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.738077</v>
+      </c>
+      <c r="J65" s="5" t="n">
+        <v>1.838033</v>
       </c>
     </row>
     <row r="66">
@@ -7003,10 +6761,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of share capital</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>Share issuance costs</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -7018,18 +6780,16 @@
         </is>
       </c>
       <c r="G66" s="5" t="n">
-        <v>2.544375</v>
+        <v>-0.149439</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>0.473817</v>
+        <v>-0.003961</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>0.738077</v>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.027853</v>
+      </c>
+      <c r="J66" s="5" t="n">
+        <v>-0.033885</v>
       </c>
     </row>
     <row r="67">
@@ -7045,14 +6805,10 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Share issuance costs</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
+          <t>Proceeds from exercise of warrants</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -7063,19 +6819,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G67" s="5" t="n">
-        <v>-0.149439</v>
-      </c>
-      <c r="H67" s="5" t="n">
-        <v>-0.003961</v>
-      </c>
-      <c r="I67" s="5" t="n">
-        <v>-0.027853</v>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="n">
+        <v>0.3625</v>
       </c>
     </row>
     <row r="68">
@@ -7091,33 +6851,39 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Payment of lease liability</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>Proceeds from exercise of options</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F68" s="5" t="n">
-        <v>-0.019</v>
-      </c>
-      <c r="G68" s="5" t="n">
-        <v>-0.019</v>
-      </c>
-      <c r="H68" s="5" t="n">
-        <v>-0.00475</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>0.07316499999999999</v>
+      </c>
+      <c r="J68" s="5" t="n">
+        <v>0.056</v>
       </c>
     </row>
     <row r="69">
@@ -7133,14 +6899,10 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Proceeds from exercise of options</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>IssuanceOfCapitalStock</t>
-        </is>
-      </c>
+          <t>Repayment of debenture loan</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -7161,13 +6923,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="5" t="n">
-        <v>0.07316499999999999</v>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="n">
+        <v>-0.201203</v>
       </c>
     </row>
     <row r="70">
@@ -7183,7 +6945,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Repayment of note payable</t>
+          <t>Share subscription received</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -7202,13 +6964,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H70" s="5" t="n">
-        <v>-0.133201</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>0.103526</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -7229,12 +6991,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Interest paid</t>
+          <t>Net cash provided by financing activities</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>InterestPaidSupplementalData</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7242,28 +7004,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F71" s="5" t="n">
+        <v>0.4612</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>2.434044</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>-0.032964</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.298941</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>0.886915</v>
+      </c>
+      <c r="J71" s="5" t="n">
+        <v>2.021445</v>
       </c>
     </row>
     <row r="72">
@@ -7279,37 +7033,33 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Share subscriptions received</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>Change in cash during the year</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F72" s="5" t="n">
+        <v>0.032075</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>0.784872</v>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>-0.826863</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>0.103526</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.203732</v>
+      </c>
+      <c r="J72" s="5" t="n">
+        <v>0.7987069999999999</v>
       </c>
     </row>
     <row r="73">
@@ -7325,12 +7075,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
+          <t>Cash, beginning of the year</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7339,21 +7089,19 @@
         </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>0.4612</v>
+        <v>0.141814</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>2.434044</v>
+        <v>0.173889</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>0.298941</v>
+        <v>0.958761</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>0.886915</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.131898</v>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>0.33563</v>
       </c>
     </row>
     <row r="74">
@@ -7369,12 +7117,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Change in cash during the year</t>
+          <t>Cash, end of the year $</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7383,21 +7131,19 @@
         </is>
       </c>
       <c r="F74" s="5" t="n">
-        <v>0.032075</v>
+        <v>0.173889</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.784872</v>
+        <v>0.958761</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>-0.826863</v>
+        <v>0.131898</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>0.203732</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.33563</v>
+      </c>
+      <c r="J74" s="5" t="n">
+        <v>1.134337</v>
       </c>
     </row>
     <row r="75">
@@ -7408,35 +7154,35 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cash, beginning of the year</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Interest free benefit on CEBA loan</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F75" s="5" t="n">
-        <v>0.141814</v>
-      </c>
-      <c r="G75" s="5" t="n">
-        <v>0.173889</v>
+        <v>-0.0138</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H75" s="5" t="n">
-        <v>0.958761</v>
-      </c>
-      <c r="I75" s="5" t="n">
-        <v>0.131898</v>
+        <v>-0.011774</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -7452,35 +7198,35 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cash, end of the year $</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Provision on trade receivable</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F76" s="5" t="n">
-        <v>0.173889</v>
-      </c>
-      <c r="G76" s="5" t="n">
-        <v>0.958761</v>
+        <v>0.007145</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H76" s="5" t="n">
-        <v>0.131898</v>
-      </c>
-      <c r="I76" s="5" t="n">
-        <v>0.33563</v>
+        <v>0.001566</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -7501,7 +7247,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Listing expense</t>
+          <t>Gain on settlement of trade payable</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -7515,13 +7261,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G77" s="5" t="n">
-        <v>2.387177</v>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>-0.0126</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -7542,12 +7288,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Amounts due to related parties</t>
+          <t>Loss on debt modification</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -7556,19 +7302,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F78" s="5" t="n">
-        <v>0.12316</v>
-      </c>
-      <c r="G78" s="5" t="n">
-        <v>0.054114</v>
-      </c>
-      <c r="H78" s="5" t="n">
-        <v>0.001647</v>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>0.00315</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -7584,12 +7334,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cash received from RTO</t>
+          <t>Amounts due from (to) related parties</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -7603,18 +7353,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G79" s="5" t="n">
-        <v>0.058108</v>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>0.001647</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>-0.057908</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -7630,12 +7378,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Accretion expense</t>
+          <t>Payment of lease liability</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -7645,17 +7393,13 @@
         </is>
       </c>
       <c r="F80" s="5" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.019</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>-0.00475</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -7676,12 +7420,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Interest</t>
+          <t>Repayment of note payable</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -7690,16 +7434,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F81" s="5" t="n">
-        <v>0.114963</v>
-      </c>
-      <c r="G81" s="5" t="n">
-        <v>0.097787</v>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>-0.133201</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -7720,30 +7466,36 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Deferred income</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>Interest paid</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F82" s="5" t="n">
-        <v>0.103364</v>
-      </c>
-      <c r="G82" s="5" t="n">
-        <v>0.025694</v>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>-0.032964</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -7764,12 +7516,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Property and equipment</t>
+          <t>Share subscriptions received</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -7778,8 +7530,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F83" s="5" t="n">
-        <v>-0.002636</v>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -7791,10 +7545,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I83" s="5" t="n">
+        <v>0.103526</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -7810,29 +7562,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Net cash used in financing activities</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Listing expense</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F84" s="5" t="n">
-        <v>-0.002636</v>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G84" s="5" t="n">
-        <v>-0.15</v>
+        <v>2.387177</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -7858,12 +7608,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Convertible notes payable</t>
+          <t>Amounts due to related parties</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -7873,17 +7623,13 @@
         </is>
       </c>
       <c r="F85" s="5" t="n">
-        <v>0.4202</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.12316</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>0.054114</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>0.001647</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -7909,7 +7655,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CEBA loan payable</t>
+          <t>Cash received from RTO</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -7918,13 +7664,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F86" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>0.058108</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -7948,18 +7694,28 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>October 31, 2021 October</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" s="5" t="n">
-        <v>0.00202</v>
+          <t>Accretion expense</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F87" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.074</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -7990,29 +7746,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Net loss for the year $</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E88" s="5" t="n">
-        <v>-0.116581</v>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F88" s="5" t="n">
-        <v>-0.097826</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.114963</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0.097787</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -8038,31 +7790,25 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="n">
-        <v>0.041384</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Deferred income</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>0.103364</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0.025694</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -8088,26 +7834,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
+          <t>Property and equipment</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F90" s="5" t="n">
-        <v>-0.00091</v>
+        <v>-0.002636</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -8138,29 +7880,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Trade payables and accrued liabilities</t>
+          <t>Net cash used in financing activities</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="n">
-        <v>0.016617</v>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F91" s="5" t="n">
-        <v>0.063059</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.002636</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>-0.15</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -8186,12 +7928,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Deferred charges</t>
+          <t>Convertible notes payable</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -8201,7 +7943,7 @@
         </is>
       </c>
       <c r="F92" s="5" t="n">
-        <v>-0.093949</v>
+        <v>0.4202</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -8232,26 +7974,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Loan receivable                                                (25,127)</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>CEBA loan payable</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F93" s="5" t="n">
-        <v>-0.119076</v>
+        <v>0.06</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -8280,24 +8018,18 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>FINANCING ACTIVITIES</t>
-        </is>
-      </c>
+      <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Subscriptions received</t>
+          <t>October 31, 2021 October</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E94" s="5" t="n">
+        <v>0.00202</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.1105</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -8328,26 +8060,24 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Issuance of common shares, net</t>
+          <t>Net loss for the year $</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>0.393398</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.116581</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>-0.097826</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -8378,24 +8108,26 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
+          <t>Stock-based compensation</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0.393398</v>
-      </c>
-      <c r="F96" s="5" t="n">
-        <v>0.1105</v>
+        <v>0.041384</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -8426,24 +8158,26 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Change in cash during the year</t>
+          <t>Prepaid expenses</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="n">
-        <v>0.334818</v>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F97" s="5" t="n">
-        <v>-0.044253</v>
+        <v>-0.00091</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -8474,24 +8208,24 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Trade payables and accrued liabilities</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>0.1</v>
+        <v>0.016617</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0.434818</v>
+        <v>0.063059</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -8522,24 +8256,22 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="n">
-        <v>0.434818</v>
+          <t>Deferred charges</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F99" s="5" t="n">
-        <v>0.390565</v>
+        <v>-0.093949</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -8570,20 +8302,26 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>disease within North America.</t>
+          <t>Loan receivable                                                (25,127)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>was   previously   conducted   by   FREmedica.   The  Company  commenced   trading   on the TSX-V under the trading symbol “FREQ” on February</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" s="5" t="n">
-        <v>0.002022</v>
+          <t>Net cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F100" s="5" t="n">
-        <v>7e-06</v>
+        <v>-0.119076</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -8614,20 +8352,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>disease within North America.</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Directors on February</t>
+          <t>Subscriptions received</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
-      <c r="E101" s="5" t="n">
-        <v>0.002022</v>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F101" s="5" t="n">
-        <v>2.8e-05</v>
+        <v>0.1105</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -8653,24 +8393,26 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sales 17 $</t>
+          <t>Issuance of common shares, net</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>0.393398</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8682,42 +8424,48 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H102" s="5" t="n">
-        <v>0.8297</v>
-      </c>
-      <c r="I102" s="5" t="n">
-        <v>1.047609</v>
-      </c>
-      <c r="J102" s="5" t="n">
-        <v>0.886467</v>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Cost of sales 13</t>
+          <t>Net cash provided by financing activities</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="n">
+        <v>0.393398</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>0.1105</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -8729,160 +8477,188 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I103" s="5" t="n">
-        <v>0.33377</v>
-      </c>
-      <c r="J103" s="5" t="n">
-        <v>0.31338</v>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Gross profit</t>
+          <t>Change in cash during the year</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>GrossProfit</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G104" s="5" t="n">
-        <v>0.434768</v>
-      </c>
-      <c r="H104" s="5" t="n">
-        <v>0.514137</v>
-      </c>
-      <c r="I104" s="5" t="n">
-        <v>0.713839</v>
-      </c>
-      <c r="J104" s="5" t="n">
-        <v>0.573087</v>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>0.334818</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>-0.044253</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Accounting and audit</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>0.1</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>0.07464999999999999</v>
-      </c>
-      <c r="G105" s="5" t="n">
-        <v>0.234343</v>
-      </c>
-      <c r="H105" s="5" t="n">
-        <v>0.24293</v>
-      </c>
-      <c r="I105" s="5" t="n">
-        <v>0.262381</v>
-      </c>
-      <c r="J105" s="5" t="n">
-        <v>0.122691</v>
+        <v>0.434818</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Advertising and marketing</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, end of year $</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>0.434818</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>0.229671</v>
-      </c>
-      <c r="G106" s="5" t="n">
-        <v>0.496467</v>
-      </c>
-      <c r="H106" s="5" t="n">
-        <v>0.573211</v>
-      </c>
-      <c r="I106" s="5" t="n">
-        <v>0.326285</v>
-      </c>
-      <c r="J106" s="5" t="n">
-        <v>0.303141</v>
+        <v>0.390565</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>disease within North America.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Consulting</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>was   previously   conducted   by   FREmedica.   The  Company  commenced   trading   on the TSX-V under the trading symbol “FREQ” on February</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" s="5" t="n">
+        <v>0.002022</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>0.025464</v>
-      </c>
-      <c r="G107" s="5" t="n">
-        <v>0.003</v>
+        <v>7e-06</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -8894,54 +8670,54 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J107" s="5" t="n">
-        <v>0.038616</v>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>disease within North America.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 7&amp;8</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Directors on February</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>2.8e-05</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H108" s="5" t="n">
-        <v>0.035148</v>
-      </c>
-      <c r="I108" s="5" t="n">
-        <v>0.032062</v>
-      </c>
-      <c r="J108" s="5" t="n">
-        <v>0.034838</v>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="109">
@@ -8950,19 +8726,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Investor relations</t>
+          <t>Sales 17 $</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -8975,17 +8747,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G109" s="5" t="n">
-        <v>0.014155</v>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H109" s="5" t="n">
-        <v>0.004355</v>
+        <v>0.8297</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>0.0343</v>
+        <v>1.047609</v>
       </c>
       <c r="J109" s="5" t="n">
-        <v>0.01118</v>
+        <v>0.886467</v>
       </c>
     </row>
     <row r="110">
@@ -8994,19 +8768,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+      <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Legal fees</t>
+          <t>Cost of sales 13</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>CostOfRevenue</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9014,20 +8784,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F110" s="5" t="n">
-        <v>0.003334</v>
-      </c>
-      <c r="G110" s="5" t="n">
-        <v>0.266798</v>
-      </c>
-      <c r="H110" s="5" t="n">
-        <v>0.01617</v>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I110" s="5" t="n">
-        <v>0.00157</v>
+        <v>0.33377</v>
       </c>
       <c r="J110" s="5" t="n">
-        <v>0.011512</v>
+        <v>0.31338</v>
       </c>
     </row>
     <row r="111">
@@ -9036,19 +8812,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+      <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Management fees 13</t>
+          <t>Gross profit</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>GrossProfit</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -9061,19 +8833,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G111" s="5" t="n">
+        <v>0.434768</v>
       </c>
       <c r="H111" s="5" t="n">
-        <v>0.386115</v>
+        <v>0.514137</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>0.40477</v>
+        <v>0.713839</v>
       </c>
       <c r="J111" s="5" t="n">
-        <v>0.5176539999999999</v>
+        <v>0.573087</v>
       </c>
     </row>
     <row r="112">
@@ -9089,33 +8859,29 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Office and general</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Accounting and audit</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F112" s="5" t="n">
-        <v>0.06524099999999999</v>
+        <v>0.07464999999999999</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.038139</v>
+        <v>0.234343</v>
       </c>
       <c r="H112" s="5" t="n">
-        <v>0.124521</v>
+        <v>0.24293</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>0.191634</v>
+        <v>0.262381</v>
       </c>
       <c r="J112" s="5" t="n">
-        <v>0.327362</v>
+        <v>0.122691</v>
       </c>
     </row>
     <row r="113">
@@ -9131,35 +8897,29 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Regulatory and transfer agent</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Advertising and marketing</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F113" s="5" t="n">
+        <v>0.229671</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.059293</v>
+        <v>0.496467</v>
       </c>
       <c r="H113" s="5" t="n">
-        <v>0.018853</v>
+        <v>0.573211</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>0.018607</v>
+        <v>0.326285</v>
       </c>
       <c r="J113" s="5" t="n">
-        <v>0.013063</v>
+        <v>0.303141</v>
       </c>
     </row>
     <row r="114">
@@ -9175,12 +8935,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Research and development</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ResearchAndDevelopment</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -9189,19 +8949,23 @@
         </is>
       </c>
       <c r="F114" s="5" t="n">
-        <v>0.017735</v>
+        <v>0.025464</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.272869</v>
-      </c>
-      <c r="H114" s="5" t="n">
-        <v>0.065191</v>
-      </c>
-      <c r="I114" s="5" t="n">
-        <v>0.001843</v>
+        <v>0.003</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J114" s="5" t="n">
-        <v>0.002019</v>
+        <v>0.038616</v>
       </c>
     </row>
     <row r="115">
@@ -9217,10 +8981,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Share-based payments 13&amp;15</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
+          <t>Depreciation and amortization 7&amp;8</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -9236,16 +9004,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H115" s="5" t="n">
+        <v>0.035148</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>0.347537</v>
+        <v>0.032062</v>
       </c>
       <c r="J115" s="5" t="n">
-        <v>0.555694</v>
+        <v>0.034838</v>
       </c>
     </row>
     <row r="116">
@@ -9261,29 +9027,35 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Wages and benefits</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F116" s="5" t="n">
-        <v>0.255008</v>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.304047</v>
+        <v>0.014155</v>
       </c>
       <c r="H116" s="5" t="n">
-        <v>0.349059</v>
+        <v>0.004355</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>0.193704</v>
+        <v>0.0343</v>
       </c>
       <c r="J116" s="5" t="n">
-        <v>0.213842</v>
+        <v>0.01118</v>
       </c>
     </row>
     <row r="117">
@@ -9299,7 +9071,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Legal fees</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -9312,24 +9084,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F117" s="5" t="n">
+        <v>0.003334</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>0.266798</v>
       </c>
       <c r="H117" s="5" t="n">
-        <v>0.010657</v>
+        <v>0.01617</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>0.039845</v>
+        <v>0.00157</v>
       </c>
       <c r="J117" s="5" t="n">
-        <v>0.075669</v>
+        <v>0.011512</v>
       </c>
     </row>
     <row r="118">
@@ -9345,12 +9113,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Operating expenses total</t>
+          <t>Management fees 13</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -9358,20 +9126,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F118" s="5" t="n">
-        <v>1.107735</v>
-      </c>
-      <c r="G118" s="5" t="n">
-        <v>2.824068</v>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H118" s="5" t="n">
-        <v>1.935399</v>
+        <v>0.386115</v>
       </c>
       <c r="I118" s="5" t="n">
-        <v>1.854538</v>
+        <v>0.40477</v>
       </c>
       <c r="J118" s="5" t="n">
-        <v>2.227281</v>
+        <v>0.5176539999999999</v>
       </c>
     </row>
     <row r="119">
@@ -9387,12 +9159,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Loss from operations</t>
+          <t>Office and general</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -9401,19 +9173,19 @@
         </is>
       </c>
       <c r="F119" s="5" t="n">
-        <v>-0.784241</v>
+        <v>0.06524099999999999</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>-2.3893</v>
+        <v>0.038139</v>
       </c>
       <c r="H119" s="5" t="n">
-        <v>-1.421262</v>
+        <v>0.124521</v>
       </c>
       <c r="I119" s="5" t="n">
-        <v>-1.140699</v>
+        <v>0.191634</v>
       </c>
       <c r="J119" s="5" t="n">
-        <v>-1.654194</v>
+        <v>0.327362</v>
       </c>
     </row>
     <row r="120">
@@ -9429,12 +9201,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Interest and other income</t>
+          <t>Regulatory and transfer agent</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -9448,16 +9220,16 @@
         </is>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.016908</v>
+        <v>0.059293</v>
       </c>
       <c r="H120" s="5" t="n">
-        <v>0.016329</v>
+        <v>0.018853</v>
       </c>
       <c r="I120" s="5" t="n">
-        <v>0.006996</v>
+        <v>0.018607</v>
       </c>
       <c r="J120" s="5" t="n">
-        <v>0.004567</v>
+        <v>0.013063</v>
       </c>
     </row>
     <row r="121">
@@ -9473,33 +9245,33 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Loan interest 11&amp;12</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr"/>
+          <t>Research and development</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>ResearchAndDevelopment</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F121" s="5" t="n">
+        <v>0.017735</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>0.272869</v>
       </c>
       <c r="H121" s="5" t="n">
-        <v>-0.05343</v>
+        <v>0.065191</v>
       </c>
       <c r="I121" s="5" t="n">
-        <v>-0.044404</v>
+        <v>0.001843</v>
       </c>
       <c r="J121" s="5" t="n">
-        <v>-0.041174</v>
+        <v>0.002019</v>
       </c>
     </row>
     <row r="122">
@@ -9515,7 +9287,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Loss on debt modification</t>
+          <t>Share-based payments 13&amp;15</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -9540,12 +9312,10 @@
         </is>
       </c>
       <c r="I122" s="5" t="n">
-        <v>-0.00315</v>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.347537</v>
+      </c>
+      <c r="J122" s="5" t="n">
+        <v>0.555694</v>
       </c>
     </row>
     <row r="123">
@@ -9561,39 +9331,29 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Wages and benefits</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F123" s="5" t="n">
+        <v>0.255008</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>0.304047</v>
+      </c>
+      <c r="H123" s="5" t="n">
+        <v>0.349059</v>
       </c>
       <c r="I123" s="5" t="n">
-        <v>-1.181257</v>
+        <v>0.193704</v>
       </c>
       <c r="J123" s="5" t="n">
-        <v>-1.690801</v>
+        <v>0.213842</v>
       </c>
     </row>
     <row r="124">
@@ -9609,12 +9369,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share 16 $</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -9632,16 +9392,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H124" s="5" t="n">
+        <v>0.010657</v>
       </c>
       <c r="I124" s="5" t="n">
-        <v>-3e-08</v>
+        <v>0.039845</v>
       </c>
       <c r="J124" s="5" t="n">
-        <v>-3e-08</v>
+        <v>0.075669</v>
       </c>
     </row>
     <row r="125">
@@ -9657,12 +9415,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Operating expenses total</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -9670,22 +9428,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F125" s="5" t="n">
+        <v>1.107735</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>35.288696</v>
+        <v>2.824068</v>
       </c>
       <c r="H125" s="5" t="n">
-        <v>38.389233</v>
+        <v>1.935399</v>
       </c>
       <c r="I125" s="5" t="n">
-        <v>44.316597</v>
+        <v>1.854538</v>
       </c>
       <c r="J125" s="5" t="n">
-        <v>51.12531</v>
+        <v>2.227281</v>
       </c>
     </row>
     <row r="126">
@@ -9701,35 +9457,33 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Deficit (8,413,294) - - - - - - - (1,181,257) (9,594,551) - - - - -</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr"/>
+          <t>Loss from operations</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F126" s="5" t="n">
+        <v>-0.784241</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>-2.3893</v>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>-1.421262</v>
       </c>
       <c r="I126" s="5" t="n">
-        <v>-11.285352</v>
+        <v>-1.140699</v>
       </c>
       <c r="J126" s="5" t="n">
-        <v>-1.690801</v>
+        <v>-1.654194</v>
       </c>
     </row>
     <row r="127">
@@ -9738,15 +9492,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
+          <t>Interest and other income</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>CostOfRevenue</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -9760,18 +9518,16 @@
         </is>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.264324</v>
+        <v>0.016908</v>
       </c>
       <c r="H127" s="5" t="n">
-        <v>0.315563</v>
+        <v>0.016329</v>
       </c>
       <c r="I127" s="5" t="n">
-        <v>0.33377</v>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.006996</v>
+      </c>
+      <c r="J127" s="5" t="n">
+        <v>0.004567</v>
       </c>
     </row>
     <row r="128">
@@ -9787,7 +9543,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Share-based payments 15</t>
+          <t>Loan interest 11&amp;12</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -9807,15 +9563,13 @@
         </is>
       </c>
       <c r="H128" s="5" t="n">
-        <v>0.109189</v>
+        <v>-0.05343</v>
       </c>
       <c r="I128" s="5" t="n">
-        <v>0.347537</v>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.044404</v>
+      </c>
+      <c r="J128" s="5" t="n">
+        <v>-0.041174</v>
       </c>
     </row>
     <row r="129">
@@ -9831,7 +9585,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Interest free benefit on CEBA loan</t>
+          <t>Loss on debt modification</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -9840,21 +9594,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F129" s="5" t="n">
-        <v>0.0138</v>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H129" s="5" t="n">
-        <v>0.011774</v>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" s="5" t="n">
+        <v>-0.00315</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -9875,35 +9631,39 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Provision on trade receivable</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F130" s="5" t="n">
-        <v>-0.007145</v>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H130" s="5" t="n">
-        <v>-0.001566</v>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" s="5" t="n">
+        <v>-1.181257</v>
+      </c>
+      <c r="J130" s="5" t="n">
+        <v>-1.690801</v>
       </c>
     </row>
     <row r="131">
@@ -9919,10 +9679,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Gain on settlement of trade payable</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>Basic and diluted loss per common share 16 $</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -9938,18 +9702,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H131" s="5" t="n">
-        <v>0.0126</v>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="J131" s="5" t="n">
+        <v>-3e-08</v>
       </c>
     </row>
     <row r="132">
@@ -9965,12 +9727,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SharesOutstanding</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -9978,22 +9740,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F132" s="5" t="n">
-        <v>-0.777586</v>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G132" s="5" t="n">
-        <v>-4.85839</v>
+        <v>35.288696</v>
       </c>
       <c r="H132" s="5" t="n">
-        <v>-1.435555</v>
+        <v>38.389233</v>
       </c>
       <c r="I132" s="5" t="n">
-        <v>-1.181257</v>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>44.316597</v>
+      </c>
+      <c r="J132" s="5" t="n">
+        <v>51.12531</v>
       </c>
     </row>
     <row r="133">
@@ -10009,14 +9771,10 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share 14 $</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Deficit (8,413,294) - - - - - - - (1,181,257) (9,594,551) - - - - -</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -10032,16 +9790,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H133" s="5" t="n">
-        <v>-4e-08</v>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I133" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-11.285352</v>
+      </c>
+      <c r="J133" s="5" t="n">
+        <v>-1.690801</v>
       </c>
     </row>
     <row r="134">
@@ -10053,12 +9811,12 @@
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Sales $</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>CostOfRevenue</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -10072,15 +9830,13 @@
         </is>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.699092</v>
+        <v>0.264324</v>
       </c>
       <c r="H134" s="5" t="n">
-        <v>0.8297</v>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.315563</v>
+      </c>
+      <c r="I134" s="5" t="n">
+        <v>0.33377</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -10101,14 +9857,10 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 7,8,13</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
+          <t>Share-based payments 15</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -10119,16 +9871,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G135" s="5" t="n">
-        <v>0.032652</v>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H135" s="5" t="n">
-        <v>0.035148</v>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.109189</v>
+      </c>
+      <c r="I135" s="5" t="n">
+        <v>0.347537</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -10149,27 +9901,25 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Management fees 14</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Interest free benefit on CEBA loan</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F136" s="5" t="n">
-        <v>0.217221</v>
-      </c>
-      <c r="G136" s="5" t="n">
-        <v>0.45746</v>
+        <v>0.0138</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H136" s="5" t="n">
-        <v>0.386115</v>
+        <v>0.011774</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -10195,7 +9945,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Share-based payments 16</t>
+          <t>Provision on trade receivable</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -10205,13 +9955,15 @@
         </is>
       </c>
       <c r="F137" s="5" t="n">
-        <v>0.037994</v>
-      </c>
-      <c r="G137" s="5" t="n">
-        <v>0.644845</v>
+        <v>-0.007145</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H137" s="5" t="n">
-        <v>0.109189</v>
+        <v>-0.001566</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -10237,7 +9989,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Loan interest</t>
+          <t>Gain on settlement of trade payable</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -10251,11 +10003,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G138" s="5" t="n">
-        <v>-0.09882100000000001</v>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H138" s="5" t="n">
-        <v>-0.05343</v>
+        <v>0.0126</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -10281,32 +10035,30 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Listing expense 4</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr"/>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F139" s="5" t="n">
+        <v>-0.777586</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>-2.387177</v>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.85839</v>
+      </c>
+      <c r="H139" s="5" t="n">
+        <v>-1.435555</v>
+      </c>
+      <c r="I139" s="5" t="n">
+        <v>-1.181257</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -10327,7 +10079,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share 15 $</t>
+          <t>Basic and diluted loss per common share 14 $</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -10340,19 +10092,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F140" s="5" t="n">
-        <v>-4e-08</v>
-      </c>
-      <c r="G140" s="5" t="n">
-        <v>-1.4e-07</v>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H140" s="5" t="n">
         <v>-4e-08</v>
       </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I140" s="5" t="n">
+        <v>-3e-08</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -10366,11 +10120,7 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>23                              (Restated)</t>
-        </is>
-      </c>
+      <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
           <t>Sales $</t>
@@ -10386,16 +10136,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F141" s="5" t="n">
-        <v>0.845488</v>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G141" s="5" t="n">
         <v>0.699092</v>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H141" s="5" t="n">
+        <v>0.8297</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -10416,17 +10166,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>23                              (Restated)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
+          <t>Depreciation and amortization 7,8,13</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>CostOfRevenue</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -10434,16 +10184,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F142" s="5" t="n">
-        <v>0.521994</v>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.264324</v>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.032652</v>
+      </c>
+      <c r="H142" s="5" t="n">
+        <v>0.035148</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -10464,17 +10214,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>23                              (Restated)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Gross profit</t>
+          <t>Management fees 14</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>GrossProfit</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -10483,15 +10233,13 @@
         </is>
       </c>
       <c r="F143" s="5" t="n">
-        <v>0.323494</v>
+        <v>0.217221</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.434768</v>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.45746</v>
+      </c>
+      <c r="H143" s="5" t="n">
+        <v>0.386115</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -10517,29 +10265,23 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 7, 8,13</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
+          <t>Share-based payments 16</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F144" s="5" t="n">
-        <v>0.016531</v>
+        <v>0.037994</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.032652</v>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.644845</v>
+      </c>
+      <c r="H144" s="5" t="n">
+        <v>0.109189</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -10565,7 +10307,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Interest</t>
+          <t>Loan interest</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -10574,16 +10316,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F145" s="5" t="n">
-        <v>0.164886</v>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.09882100000000001</v>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.09882100000000001</v>
+      </c>
+      <c r="H145" s="5" t="n">
+        <v>-0.05343</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -10609,14 +10351,10 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Listing expense 4</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -10628,7 +10366,7 @@
         </is>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.016908</v>
+        <v>-2.387177</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -10654,30 +10392,32 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>(Expressed in Canadian dollar)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Note October 31, 2021 October</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" s="5" t="n">
-        <v>0.00202</v>
+          <t>Basic and diluted loss per common share 15 $</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F147" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4e-08</v>
+      </c>
+      <c r="G147" s="5" t="n">
+        <v>-1.4e-07</v>
+      </c>
+      <c r="H147" s="5" t="n">
+        <v>-4e-08</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -10698,25 +10438,29 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>23                              (Restated)</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Administrative Fees 8 $</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" s="5" t="n">
-        <v>0.0063</v>
+          <t>Sales $</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F148" s="5" t="n">
-        <v>0.0189</v>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.845488</v>
+      </c>
+      <c r="G148" s="5" t="n">
+        <v>0.699092</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -10742,17 +10486,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>23                              (Restated)</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>CostOfRevenue</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -10761,12 +10505,10 @@
         </is>
       </c>
       <c r="F149" s="5" t="n">
-        <v>0.007324</v>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.521994</v>
+      </c>
+      <c r="G149" s="5" t="n">
+        <v>0.264324</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -10792,31 +10534,29 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>23                              (Restated)</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Marketing and promotion</t>
+          <t>Gross profit</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E150" s="5" t="n">
-        <v>0.000595</v>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F150" s="5" t="n">
+        <v>0.323494</v>
+      </c>
+      <c r="G150" s="5" t="n">
+        <v>0.434768</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -10842,29 +10582,29 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Office and miscellaneous</t>
+          <t>Depreciation and amortization 7, 8,13</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E151" s="5" t="n">
-        <v>0.002791</v>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F151" s="5" t="n">
-        <v>0.003116</v>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.016531</v>
+      </c>
+      <c r="G151" s="5" t="n">
+        <v>0.032652</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -10890,29 +10630,25 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E152" s="5" t="n">
-        <v>0.035544</v>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F152" s="5" t="n">
-        <v>0.048002</v>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.164886</v>
+      </c>
+      <c r="G152" s="5" t="n">
+        <v>0.09882100000000001</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -10938,29 +10674,31 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Regulatory fees</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E153" s="5" t="n">
-        <v>0.025597</v>
-      </c>
-      <c r="F153" s="5" t="n">
-        <v>0.017938</v>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G153" s="5" t="n">
+        <v>0.016908</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -10986,22 +10724,20 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>(Expressed in Canadian dollar)</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Share-based compensation 7</t>
+          <t>Note October 31, 2021 October</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" s="5" t="n">
-        <v>0.041384</v>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.00202</v>
+      </c>
+      <c r="F154" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -11037,19 +10773,15 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Transfer agent fees</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Administrative Fees 8 $</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
       <c r="E155" s="5" t="n">
-        <v>0.00437</v>
+        <v>0.0063</v>
       </c>
       <c r="F155" s="5" t="n">
-        <v>0.003045</v>
+        <v>0.0189</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -11085,19 +10817,21 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Total Expenses</t>
+          <t>Consulting fees</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E156" s="5" t="n">
-        <v>0.116581</v>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F156" s="5" t="n">
-        <v>0.098325</v>
+        <v>0.007324</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -11128,26 +10862,26 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Interest Income</t>
+          <t>Marketing and promotion</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F157" s="5" t="n">
-        <v>0.000499</v>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="n">
+        <v>0.000595</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -11178,24 +10912,24 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
+          <t>Office and miscellaneous</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>-0.116581</v>
+        <v>0.002791</v>
       </c>
       <c r="F158" s="5" t="n">
-        <v>-0.097826</v>
+        <v>0.003116</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -11226,24 +10960,24 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Loss per share</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>– Basic and Diluted $</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>-8e-08</v>
+        <v>0.035544</v>
       </c>
       <c r="F159" s="5" t="n">
-        <v>-3e-08</v>
+        <v>0.048002</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -11274,20 +11008,24 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Weighted average shares outstanding</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>– Basic and Diluted</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
+          <t>Regulatory fees</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E160" s="5" t="n">
-        <v>1.406181</v>
+        <v>0.025597</v>
       </c>
       <c r="F160" s="5" t="n">
-        <v>3.181341</v>
+        <v>0.017938</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -11318,20 +11056,22 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Note       Shares          Amount      Reserves                Deficit         Total Equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Balance at October 31, 2019 2,000,000 $ 100,000 $ - $</t>
+          <t>Share-based compensation 7</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" s="5" t="n">
-        <v>0.09461700000000001</v>
-      </c>
-      <c r="F161" s="5" t="n">
-        <v>-0.005383</v>
+        <v>0.041384</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -11362,22 +11102,24 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Note       Shares          Amount      Reserves                Deficit         Total Equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Issuance of shares for cash 7 2,000,000 100,000 -</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>Transfer agent fees</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E162" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.00437</v>
+      </c>
+      <c r="F162" s="5" t="n">
+        <v>0.003045</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -11408,22 +11150,24 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Note       Shares          Amount      Reserves                Deficit         Total Equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Initial Public Offering (“IPO”) 7 2,000,000 200,000 -</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
+          <t>Total Expenses</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E163" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.116581</v>
+      </c>
+      <c r="F163" s="5" t="n">
+        <v>0.098325</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -11454,22 +11198,26 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Note       Shares          Amount      Reserves                Deficit         Total Equity</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Shares issued for private placement 7 1,181,341 177,200 -</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" s="5" t="n">
-        <v>0.1772</v>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F164" s="5" t="n">
+        <v>0.000499</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -11500,22 +11248,24 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Note       Shares          Amount      Reserves                Deficit         Total Equity</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Share issuance costs 7 - (83,802) -</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E165" s="5" t="n">
-        <v>-0.083802</v>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.116581</v>
+      </c>
+      <c r="F165" s="5" t="n">
+        <v>-0.097826</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -11546,24 +11296,24 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Note       Shares          Amount      Reserves                Deficit         Total Equity</t>
+          <t>Loss per share</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Fair value of agent’s warrants 7 - (10,419) 10,419</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>– Basic and Diluted $</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="n">
+        <v>-8e-08</v>
+      </c>
+      <c r="F166" s="5" t="n">
+        <v>-3e-08</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -11594,22 +11344,20 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Note       Shares          Amount      Reserves                Deficit         Total Equity</t>
+          <t>Weighted average shares outstanding</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Stock-based compensation 7 - - 41,384</t>
+          <t>– Basic and Diluted</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" s="5" t="n">
-        <v>0.041384</v>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.406181</v>
+      </c>
+      <c r="F167" s="5" t="n">
+        <v>3.181341</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -11645,19 +11393,15 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Net loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Balance at October 31, 2019 2,000,000 $ 100,000 $ - $</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
       <c r="E168" s="5" t="n">
-        <v>-0.116581</v>
+        <v>0.09461700000000001</v>
       </c>
       <c r="F168" s="5" t="n">
-        <v>-0.116581</v>
+        <v>-0.005383</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -11693,15 +11437,17 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Balance at October 31, 2020 7,181,341 482,979 51,803</t>
+          <t>Issuance of shares for cash 7 2,000,000 100,000 -</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" s="5" t="n">
-        <v>0.412818</v>
-      </c>
-      <c r="F169" s="5" t="n">
-        <v>-0.121964</v>
+        <v>0.1</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -11737,32 +11483,356 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Balance at October 31, 2021 7,181,341 $ 482,979 $ 51,803 $</t>
+          <t>Initial Public Offering (“IPO”) 7 2,000,000 200,000 -</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Note       Shares          Amount      Reserves                Deficit         Total Equity</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Shares issued for private placement 7 1,181,341 177,200 -</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" s="5" t="n">
+        <v>0.1772</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Note       Shares          Amount      Reserves                Deficit         Total Equity</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Share issuance costs 7 - (83,802) -</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" s="5" t="n">
+        <v>-0.083802</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Note       Shares          Amount      Reserves                Deficit         Total Equity</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Fair value of agent’s warrants 7 - (10,419) 10,419</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Note       Shares          Amount      Reserves                Deficit         Total Equity</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Stock-based compensation 7 - - 41,384</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" s="5" t="n">
+        <v>0.041384</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Note       Shares          Amount      Reserves                Deficit         Total Equity</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Net loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E175" s="5" t="n">
+        <v>-0.116581</v>
+      </c>
+      <c r="F175" s="5" t="n">
+        <v>-0.116581</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Note       Shares          Amount      Reserves                Deficit         Total Equity</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Balance at October 31, 2020 7,181,341 482,979 51,803</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" s="5" t="n">
+        <v>0.412818</v>
+      </c>
+      <c r="F176" s="5" t="n">
+        <v>-0.121964</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Note       Shares          Amount      Reserves                Deficit         Total Equity</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Balance at October 31, 2021 7,181,341 $ 482,979 $ 51,803 $</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" s="5" t="n">
         <v>0.314992</v>
       </c>
-      <c r="F170" s="5" t="n">
+      <c r="F177" s="5" t="n">
         <v>-0.21979</v>
       </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
         <is>
           <t>-</t>
         </is>
